--- a/data/daily/2026-10/2026-10-09.xlsx
+++ b/data/daily/2026-10/2026-10-09.xlsx
@@ -1170,14 +1170,164 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,160 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,27 +1425,177 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,204 +1603,54 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 피로회복 — 피곤하고 지칠 때 하나씩 섭취하면 기운이 나고 활력이 생김</t>
+          <t>뛰어난 피로회복 — 피곤하고 지칠 때 하나씩 섭취하면 활력이 생김</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로 제격 — 패키지가 깔끔하고 정성스러워 선물로 주고받을 때 만족도가 높음</t>
+          <t>우수한 선물용 구성 — 건강을 챙겨주는 느낌을 주어 선물용으로 제격임</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>향기로운 증정차 — 증정품으로 제공되는 티백 차의 향이 은은하고 매우 좋음</t>
+          <t>매력적인 증정품 — 함께 증정되는 로네펠트 티백의 향과 맛이 훌륭함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2655,27 +2655,31 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15552</v>
+        <v>15555</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>체력 및 집중력 개선 — 꾸준히 복용 시 피로가 줄어들고 오전에 집중이 잘되는 느낌을 받음</t>
+          <t>간편한 섭취 방법 — 물 없이 언제 어디서나 편리하게 복용할 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>예쁜 선물용 포장 — 포장 디자인이 예뻐서 선물용으로 받았을 때 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>예쁜 포장 패키지 — 디자인과 포장이 예뻐 선물받을 때 기분이 아주 좋아짐</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>확실한 피로개선 — 지치고 피곤할 때 에너지를 충전하는 데 도움을 줌</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송이 도착하는 데 10일이나 소요되어 선물 전달 시 곤란함</t>
+          <t>심각한 배송 지연 — 배송이 최대 10일까지 늦어져 선물 전달에 차질이 생김</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 제품의 가격대가 다소 높게 책정되어 다소 아쉽게 느껴짐</t>
+          <t>다소 부담스러운 가격 — 타 비타민 제품에 비해 가격대가 다소 높게 느껴짐</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -2722,22 +2726,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 — 복용 후 몸의 활력이 달라지는 것이 느껴지며 다음 날 피로감이 감소함</t>
+          <t>빠른 활력 충전 — 복용 후 몸의 활력이 달라지고 피로 회복 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>꼼꼼한 포장 배송 — 배송 시 꼼꼼하고 안전하게 포장되어 수령 시 만족스러움</t>
+          <t>꼼꼼한 배송 포장 — 파손 없이 안전하고 정성스럽게 포장되어 배송됨</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>합리적인 구매 가격 — 공식 수입품임에도 비교적 저렴하고 합리적인 가격에 구매가 가능함</t>
+          <t>합리적인 구매 가격 — 정식 수입품을 상대적으로 저렴한 가격에 구매할 수 있음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>아쉬운 액상 맛 — 제형의 농도가 진하고 액상 특성상 맛 자체는 다소 아쉬움</t>
+          <t>아쉬운 액상 맛 — 타 액상 영양제처럼 맛 자체는 뛰어난 편이 아님</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2785,17 +2789,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 새콤달콤한 맛의 젤리 형태로 되어 있어 간식처럼 맛있게 먹기 좋음</t>
+          <t>맛있는 젤리 형태 — 새콤달콤한 맛과 젤리 제형으로 부담 없이 간식처럼 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>편리한 섭취 방식 — 알약을 잘 넘기지 못하는 사람도 부담 없이 매일 챙겨 먹기 편함</t>
+          <t>편리한 영양 섭취 — 알약을 삼키기 힘들어하는 사람도 쉽게 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>귀여운 증정품 구성 — 감귤 모양의 패키지와 함께 동봉된 귀여운 키캡 만족도가 높음</t>
+          <t>귀엽고 센스있는 패키지 — 감귤 모양 디자인의 손잡이 패키지와 함께 증정된 키캡이 무척 귀여움</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2840,26 +2844,26 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성과 편의 — 개별 포장 및 마시는 제형으로 가방에 넣어 다니며 물 없이 편하게 섭취함</t>
+          <t>빠른 피로 회복 — 섭취 후 오후 시간대 체력 저하와 눈의 피로감이 덜해짐</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>빠른 피로회복 효과 — 복용 후 오후의 지친 체력이나 눈의 피로감이 덜해지는 것이 느껴짐</t>
+          <t>우수한 휴대성 — 개별 포장이 견고하여 외출 시 가방에 넣어 다니기 편리함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>합리적인 가격 — 다른 플랫폼 대비 저렴한 가격대로 구성되어 만족함</t>
+          <t>간편한 마시는 형태 — 물 없이도 어디서든 편하게 마실 수 있어 섭취가 용이함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>다소 부실한 포장 — 전용 쇼핑백 없이 제품 박스만 덜렁 배송되어 선물용 포장으로는 아쉬움</t>
+          <t>아쉬운 포장 서비스 — 쇼핑백이 제공되지 않고 상자에만 담겨 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2903,26 +2907,26 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8744</v>
+        <v>8745</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>편리한 복합 제형 — 알약과 마시는 음료가 함께 세트로 구성되어 따로 챙겨 먹는 번거로움이 없음</t>
+          <t>간편한 휴대와 섭취 — 소포장 및 개별 포장 형태로 가방에 넣어 휴대하며 섭취하기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지가 깔끔하고 고급스러워 지인들에게 생일 선물로 주기에 적합함</t>
+          <t>부드러운 목넘김과 맛 — 비타민 맛이 부담스럽지 않아 꾸준히 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>알찬 단독 구성 — 추가 증정이 포함된 선물하기 전용 구성이라 알차게 느껴짐</t>
+          <t>고급스러운 패키지 — 음료와 알약 세트 구성으로 포장이 깔끔하고 세련됨</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>다소 아쉬운 부피감 — 포장 크기가 콤팩트하여 시각적으로 매우 풍성한 느낌을 주지는 않음</t>
+          <t>부족한 볼륨감 — 소포장 구성 특성상 선물할 때 풍성한 느낌이 다소 덜함</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2970,17 +2974,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 정성 가득한 박스와 전용 쇼핑백이 동봉되어 품격 있는 선물로 제격임</t>
+          <t>품격 있는 명절 포장 — 고급스러운 박스와 전용 쇼핑백 덕분에 선물용으로 매우 적합함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>편리한 휴대와 섭취 — 한 병씩 포장되어 출근할 때 가방에 챙겨 다니며 간편하게 마시기 좋음</t>
+          <t>부담 없는 수량 — 10일분 구성으로 처음 접하는 사람도 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>환절기 면역력 관리 — 체력이 저하되는 바쁜 시기에 면역력과 활력을 키우는 데 유용함</t>
+          <t>간편한 데일리 복용 — 한 병씩 개별 포장되어 바쁜 출근 시간에도 쉽게 챙길 수 있음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3029,17 +3033,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>확실한 컨디션 회복 — 감기나 잦은 피로에 시달릴 때 복용하면 몸이 덜 피곤하고 활력이 생김</t>
+          <t>독특하고 신선한 제형 — 액상과 분말이 결합된 이색적인 패키지로 섭취가 흥미로움</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>신기하고 편한 용기 — 액상과 분말이 결합한 신기한 포장이면서도 전혀 섭취에 불편함이 없음</t>
+          <t>거부감 없는 맛 — 다른 건강식품에 비해 맛이 좋아 간편하고 즐겁게 복용 가능함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>맛있는 맛 — 맛이 좋아 영양제를 거부감 없이 맛있고 편하게 섭취 가능함</t>
+          <t>확실한 컨디션 개선 — 섭취 후 피로감이 줄어들고 몸의 활력이 생기는 것을 느낌</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3088,17 +3092,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤 선택 — 남성과 여성 전용 포뮬러를 따로 선택하여 필요한 영양소를 실속 있게 섭취함</t>
+          <t>성별 맞춤형 설계 — 남성과 여성에 필요한 영양 성분이 각각 구분되어 선택에 용이함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>비린내 없는 진한 맛 — 비타민 특유의 쓰거나 비린 맛없이 진하고 묵직하여 삼키기 수월함</t>
+          <t>쓴맛 없는 편안함 — 특유의 쓴맛이 없어 거부감 없이 편하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>높은 선물 만족도 — 고급 포장 패키지로 구성되어 있어 지인 건강 응원용 선물로 인기가 높음</t>
+          <t>풍부한 영양소 함량 — 기존 오쏘몰 이뮨 라인 대비 영양소가 다량 함유되어 있음</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3147,18 +3151,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>믿을 수 있는 원료 — 영국산 비타민C 원료를 사용하여 품질 면에서 더욱 안심하고 섭취함</t>
+          <t>신뢰할 수 있는 원산지 — 영국산 고품질 비타민C 원료를 사용하여 안심하고 복용 가능함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>확실한 체감 효과 — 매일 섭취 시 피부 상태 개선 및 체력 관리에 긍정적인 영향이 느껴짐</t>
+          <t>확실한 피부 컨디션 개선 — 복용 시 피부 상태와 신체 활력이 개선되는 것을 체감함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>매우 신맛과 아쉬운 맛 — 가루 제형 특유의 자극적인 신맛과 씁쓸함으로 인해 먹기가 힘듦</t>
+          <t>너무 자극적인 신맛 — 가루 제형에 산도가 매우 높아 섭취 시 신맛과 쓴맛의 거부감이 큼</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3202,24 +3206,24 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>훌륭하고 맛있는 맛 — 효소 제품임에도 특유의 거북한 향이 전혀 없고 아주 맛있음</t>
+          <t>알찬 굿즈 및 사은품 — 포토카드와 엽서, 고단백질바 등 풍성하고 퀄리티 높은 사은품을 제공함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>풍성한 콜라보 구성 — 아이돌 포토카드, 엽서 및 증정 단백질바까지 다채로운 구성품이 함께 제공됨</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>다소 지연된 배송 — 주문 이후 수령할 때까지 대기 시간이 다소 길어 아쉬움</t>
-        </is>
-      </c>
+          <t>거부감 없는 뛰어난 맛 — 효소 특유의 쿰쿰함 없이 맛있고 다양한 맛으로 즐길 수 있음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>깔끔하고 안전한 포장 — 내용물이 훼손되지 않도록 견고하게 잘 밀봉되어 배송됨</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3265,20 +3269,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>뛰어난 소화 개선 — 밀가루나 무거운 식사를 한 후 섭취하면 더부룩한 속이 한결 편안해짐</t>
+          <t>탁월한 소화 개선 효과 — 밀가루 섭취 후 속이 더부룩할 때 복용하면 속이 편안해짐</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>구수한 고구마 맛 — 역한 맛없이 달콤하고 구수한 고구마 맛이 나서 온 가족이 맛있게 먹음</t>
+          <t>구수하고 친숙한 고구마맛 — 시큼하지 않고 구수한 고구마 맛이 나서 호불호 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>알찬 사은품 혜택 — 파로 곡물바 및 차 제품이 증정품으로 추가 포함되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>넉넉한 사은품 증정 — 구매 시 견과류바와 추가 포가 증정되어 구성이 풍성함</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>정가 구매 시의 부담감 — 할인을 하지 않을 때는 가격대가 다소 높게 느껴져 아쉬움</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3324,18 +3332,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>눈부신 오간자 포장 — 오간자 에디션 포장과 세트 플리츠백이 극도로 화려하고 예뻐 감격스러움</t>
+          <t>감동을 주는 고급 포장 — 오간자 에디션과 플리츠백 등 패키지가 아주 세련되어 열어보는 즐거움이 있음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>비림 없는 맛과 효과 — 콜라겐 특유의 비린 맛 없이 상큼하고 맛있으며 피부 탄력 및 피로에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>맛있는 액상 콜라겐 — 비린 맛 없이 상큼하고 맛있어서 꾸준히 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>만족스러운 피로 완화 — 복용 시 평소보다 피로를 느끼는 빈도가 줄어드는 느낌을 받음</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>꽤 비싼 가격대 — 정가가 다소 높게 느껴져 주로 할인 행사 기간을 기다려 구매하게 됨</t>
+          <t>다소 값비싼 가격대 — 정가 기준으로 가격 부담이 커 할인 기간에만 구매를 고려하게 됨</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3383,22 +3395,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 맛 — 퍽퍽함이나 비린내가 전혀 느껴지지 않으며 식감이 매우 부드러움</t>
+          <t>촉촉하고 부드러운 육질 — 닭가슴살 특유의 퍽퍽함 없이 수분감이 있어 섭취하기 좋음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다채로운 양념 소스 — 떡볶이맛 등 다이어트 식단이라는 생각이 안 들 정도로 다양한 맛을 맛있게 즐김</t>
+          <t>훌륭한 소스 맛과 다양성 — 떡볶이 맛 등 질리지 않는 다양한 소스로 구성되어 맛있는 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>훌륭한 가성비 — 할인 혜택 적용 시 많은 수량의 구성품을 저렴한 가격에 쟁여두기 좋음</t>
+          <t>매력적인 특가 구성 — 다양한 구성을 타 유통 채널 대비 합리적인 가격으로 구매 가능함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>선호 품목 누락 아쉬움 — 파우치형 그릴 제품 등 선호도가 높은 일부 라인업이 구성에서 빠져 아쉽음</t>
+          <t>일부 선호 종류의 누락 — 맛있는 파우치 그릴 제품 등 선호도가 높은 특정 구성이 빠져 있어 아쉬움</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3446,22 +3458,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>신속한 숙취 완화 — 음주 전후 섭취 시 다음 날 머리가 무겁거나 피로한 숙취 증상이 눈에 띄게 줄어듦</t>
+          <t>뛰어난 숙취 해소 효능 — 음주 전후 섭취 시 다음 날 아침 피로와 두통 등 숙취가 눈에 띄게 줄어듦</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>편리한 휴대와 포장 — 가볍고 작은 낱개 스틱으로 설계되어 가방에 넣고 다니다가 물 없이 짜 먹기 좋음</t>
+          <t>고급스러운 보라빛 선물팩 — 전용 쇼핑백과 리본 디테일이 갖춰져 있어 선물하기에 대단히 품격 있음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>품격 있는 패키지 — 고급스러운 보라색 박스 및 리본 끈 리플릿 포장으로 선물용 가치가 우수함</t>
+          <t>휴대에 용이한 스틱형 — 작고 가벼운 개별 스틱으로 가방이나 주머니에 넣어 다닐 수 있음</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>쓴맛에 대한 호불호 — 쌍화탕이나 칡, 헛개 같은 한약재 맛이 다소 진하게 풍겨 호불호가 갈릴 수 있음</t>
+          <t>호불호 갈리는 한약 맛 — 쌍화탕이나 약재 같은 씁쓸하고 진한 맛이 느껴져 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3509,22 +3521,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 아침에 가뿐하게 기상할 수 있고 운동할 때 지치지 않아 컨디션에 큰 도움을 줌</t>
+          <t>완벽한 활력 영양 조합 — 활력 충전용 아르기닌과 간 건강용 밀크씨슬을 효율적으로 한 번에 챙길 수 있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>완벽한 성분 조합 — 지친 간을 위한 밀크씨슬과 활력 증진용 아르기닌을 한 번에 챙길 수 있는 알찬 세트임</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>넉넉한 용량 — 2개월분의 넉넉한 수량으로 구성되어 장기적인 관리가 수월함</t>
-        </is>
-      </c>
+          <t>우수한 일상 피로 개선 — 섭취 후 아침 기상이 가벼워지며 운동 집중력 향상에 큰 도움을 줌</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>쇼핑백 마감 불량 — 선물용으로 동봉되는 전용 쇼핑백의 손잡이 끈이 조립되지 않은 채 누락되어 배송됨</t>
+          <t>사은품 쇼핑백 마감 불량 — 동봉된 선물용 쇼핑백의 손잡이 끈이 누락되어 오는 배송 하자가 발생함</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3533,7 +3541,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3541,53 +3549,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>타이거모닝</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31,500원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/13586002</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007104254_bd7666cf9044472bb3ec327d17c35b29.png</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>부드럽고 쫄깃한 식감 — 닭가슴살 본연의 퍽퍽함을 탈피하여 쫄깃하고 속이 매우 부드러움</t>
+          <t>상큼한 과일생강 조합 — 생강 외 사과, 레몬 등이 혼합되어 과일주스처럼 상큼하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>다양한 맛과 적당한 간 — 간이 짜지 않고 적절하며 볼 형태와 소스 타입이 다양해 식단 관리가 지루하지 않음</t>
+          <t>감각적이고 귀여운 병 — 한 손에 쏙 들어오는 미니 보틀 형태로 디자인이 깜찍해 소장 가치가 높음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>빠른 조리 편의성 — 전자레인지에 간단히 데우기만 하면 바로 먹을 수 있어 식사 시간이 단축됨</t>
+          <t>환절기 호흡기 관리 도움 — 목 잠김 현상이 줄어들고 몸을 따뜻하게 보호해 비염과 환절기 건강 관리에 유용함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>약간의 배송 지연 — 주문 후 실제 수령하기까지 배송 속도가 다른 곳보다 다소 느렸음</t>
+          <t>다소 강한 생강의 자극 — 생강 함량이 높아 톡 쏘는 찡한 매운맛에 대해 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3596,7 +3604,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3604,7 +3612,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3614,38 +3622,38 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1179</v>
+        <v>1909</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 맛 — 매실, 알로에, 요구르트 등 역함이나 인공적인 향 없이 음료수처럼 맛있음</t>
+          <t>입자의 우수한 용해성 — 가루 뭉침 현상 없이 찬물이나 프로틴 음료에 부드럽고 빠르게 잘 녹음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>운동 집중력 상승 — 수분 및 전해질 보충으로 운동 수행 능력과 에너지가 향상됨</t>
+          <t>확실한 운동 능력 상승 — 몇 주간 꾸준히 섭취 시 운동 수행 횟수가 증가하고 근육 피로 회복이 빨라짐</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>물에 잘 녹는 분말 — 차가운 물에도 가루 뭉침 없이 부드럽게 잘 풀려 음용하기 편함</t>
+          <t>편리한 스쿱 내장 구성 — 통 내부에 전용 계량 스쿱이 들어있어 매일 정량 복용하기 편리함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3663,51 +3671,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>31,500원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>비린 맛없는 깔끔함 — 프로틴 특유의 텁텁하고 비린 뒷맛이 전혀 느껴지지 않고 청량함</t>
+          <t>부드럽고 촉촉한 육질 — 수분감을 가득 머금어 전혀 퍽퍽하지 않고 쫄깃하고 촉촉함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>포만감 가득한 든든함 — 운동 후 혹은 간식이 당길 때 섭취하면 배가 든든하게 채워져 식단에 유용함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>달콤하고 부드러운 맛 — 모카초콜릿, 딸기초코 등 시판 초코우유나 커피음료와 유사한 훌륭한 맛을 구현함</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>간편한 한 입 크기 볼 — 닭가슴살볼이 한 입 크기로 만들어져 샐러드나 도시락 반찬으로 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>아쉬운 배송 지연 — 주문 후 수령하기까지 배송에 다소 시간이 소요되어 아쉬움</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3722,55 +3730,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>타이거모닝</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13586002</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007104254_bd7666cf9044472bb3ec327d17c35b29.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>1179</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>상큼하고 부드러운 맛 — 생강 함량이 높음에도 사과, 파인애플 등이 섞여 과일 주스처럼 섭취가 부드러움</t>
+          <t>역대급으로 훌륭한 맛 — 매실, 알로에, 요구르트 등 맛의 완성도가 매우 높아 물처럼 부담 없이 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>기상 시 에너지 충전 — 공복에 섭취 시 위에 부담이 없고 온몸이 따뜻해지며 수면 부족 피로를 깨워줌</t>
+          <t>뛰어난 가루 풀림성 — 미세한 가루가 찬물에도 뭉치지 않고 빠르게 녹아들어 섭취가 용이함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>소장하고 싶은 보틀 — 앙증맞고 귀여운 미니 병 형태로 보관이 편리하고 섭취 시 기분 전환에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>매운 향에 따른 호불호 — 생강 본연의 톡 쏘는 아린 맛이 뒤에 남아 어린아이나 입맛에 따라 맵게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>대용량의 합리적 가격 — 오랫동안 복용할 수 있는 넉넉한 분량이 제공되어 가성비가 아주 우수함</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4095,7 +4099,7 @@
         <v>16239</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15552</v>
+        <v>15555</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3400</v>
@@ -4104,10 +4108,10 @@
         <v>6510</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8744</v>
+        <v>8745</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>812</v>
@@ -4130,70 +4134,71 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로회복 — 피곤하고 지칠 때 하나씩 섭취하면 기운이 나고 활력이 생김
-선물용으로 제격 — 패키지가 깔끔하고 정성스러워 선물로 주고받을 때 만족도가 높음
-향기로운 증정차 — 증정품으로 제공되는 티백 차의 향이 은은하고 매우 좋음</t>
+          <t>뛰어난 피로회복 — 피곤하고 지칠 때 하나씩 섭취하면 활력이 생김
+우수한 선물용 구성 — 건강을 챙겨주는 느낌을 주어 선물용으로 제격임
+매력적인 증정품 — 함께 증정되는 로네펠트 티백의 향과 맛이 훌륭함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>체력 및 집중력 개선 — 꾸준히 복용 시 피로가 줄어들고 오전에 집중이 잘되는 느낌을 받음
-예쁜 선물용 포장 — 포장 디자인이 예뻐서 선물용으로 받았을 때 만족도가 높음</t>
+          <t>간편한 섭취 방법 — 물 없이 언제 어디서나 편리하게 복용할 수 있음
+예쁜 포장 패키지 — 디자인과 포장이 예뻐 선물받을 때 기분이 아주 좋아짐
+확실한 피로개선 — 지치고 피곤할 때 에너지를 충전하는 데 도움을 줌</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 — 복용 후 몸의 활력이 달라지는 것이 느껴지며 다음 날 피로감이 감소함
-꼼꼼한 포장 배송 — 배송 시 꼼꼼하고 안전하게 포장되어 수령 시 만족스러움
-합리적인 구매 가격 — 공식 수입품임에도 비교적 저렴하고 합리적인 가격에 구매가 가능함</t>
+          <t>빠른 활력 충전 — 복용 후 몸의 활력이 달라지고 피로 회복 효과가 뛰어남
+꼼꼼한 배송 포장 — 파손 없이 안전하고 정성스럽게 포장되어 배송됨
+합리적인 구매 가격 — 정식 수입품을 상대적으로 저렴한 가격에 구매할 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 새콤달콤한 맛의 젤리 형태로 되어 있어 간식처럼 맛있게 먹기 좋음
-편리한 섭취 방식 — 알약을 잘 넘기지 못하는 사람도 부담 없이 매일 챙겨 먹기 편함
-귀여운 증정품 구성 — 감귤 모양의 패키지와 함께 동봉된 귀여운 키캡 만족도가 높음</t>
+          <t>맛있는 젤리 형태 — 새콤달콤한 맛과 젤리 제형으로 부담 없이 간식처럼 먹기 좋음
+편리한 영양 섭취 — 알약을 삼키기 힘들어하는 사람도 쉽게 챙겨 먹을 수 있음
+귀엽고 센스있는 패키지 — 감귤 모양 디자인의 손잡이 패키지와 함께 증정된 키캡이 무척 귀여움</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성과 편의 — 개별 포장 및 마시는 제형으로 가방에 넣어 다니며 물 없이 편하게 섭취함
-빠른 피로회복 효과 — 복용 후 오후의 지친 체력이나 눈의 피로감이 덜해지는 것이 느껴짐
-합리적인 가격 — 다른 플랫폼 대비 저렴한 가격대로 구성되어 만족함</t>
+          <t>빠른 피로 회복 — 섭취 후 오후 시간대 체력 저하와 눈의 피로감이 덜해짐
+우수한 휴대성 — 개별 포장이 견고하여 외출 시 가방에 넣어 다니기 편리함
+간편한 마시는 형태 — 물 없이도 어디서든 편하게 마실 수 있어 섭취가 용이함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>편리한 복합 제형 — 알약과 마시는 음료가 함께 세트로 구성되어 따로 챙겨 먹는 번거로움이 없음
-고급스러운 포장 — 패키지가 깔끔하고 고급스러워 지인들에게 생일 선물로 주기에 적합함
-알찬 단독 구성 — 추가 증정이 포함된 선물하기 전용 구성이라 알차게 느껴짐</t>
+          <t>간편한 휴대와 섭취 — 소포장 및 개별 포장 형태로 가방에 넣어 휴대하며 섭취하기 좋음
+부드러운 목넘김과 맛 — 비타민 맛이 부담스럽지 않아 꾸준히 챙겨 먹기 적합함
+고급스러운 패키지 — 음료와 알약 세트 구성으로 포장이 깔끔하고 세련됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 정성 가득한 박스와 전용 쇼핑백이 동봉되어 품격 있는 선물로 제격임
-편리한 휴대와 섭취 — 한 병씩 포장되어 출근할 때 가방에 챙겨 다니며 간편하게 마시기 좋음
-환절기 면역력 관리 — 체력이 저하되는 바쁜 시기에 면역력과 활력을 키우는 데 유용함</t>
+          <t>품격 있는 명절 포장 — 고급스러운 박스와 전용 쇼핑백 덕분에 선물용으로 매우 적합함
+부담 없는 수량 — 10일분 구성으로 처음 접하는 사람도 부담 없이 섭취 가능함
+간편한 데일리 복용 — 한 병씩 개별 포장되어 바쁜 출근 시간에도 쉽게 챙길 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>확실한 컨디션 회복 — 감기나 잦은 피로에 시달릴 때 복용하면 몸이 덜 피곤하고 활력이 생김
-신기하고 편한 용기 — 액상과 분말이 결합한 신기한 포장이면서도 전혀 섭취에 불편함이 없음
-맛있는 맛 — 맛이 좋아 영양제를 거부감 없이 맛있고 편하게 섭취 가능함</t>
+          <t>독특하고 신선한 제형 — 액상과 분말이 결합된 이색적인 패키지로 섭취가 흥미로움
+거부감 없는 맛 — 다른 건강식품에 비해 맛이 좋아 간편하고 즐겁게 복용 가능함
+확실한 컨디션 개선 — 섭취 후 피로감이 줄어들고 몸의 활력이 생기는 것을 느낌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 선택 — 남성과 여성 전용 포뮬러를 따로 선택하여 필요한 영양소를 실속 있게 섭취함
-비린내 없는 진한 맛 — 비타민 특유의 쓰거나 비린 맛없이 진하고 묵직하여 삼키기 수월함
-높은 선물 만족도 — 고급 포장 패키지로 구성되어 있어 지인 건강 응원용 선물로 인기가 높음</t>
+          <t>성별 맞춤형 설계 — 남성과 여성에 필요한 영양 성분이 각각 구분되어 선택에 용이함
+쓴맛 없는 편안함 — 특유의 쓴맛이 없어 거부감 없이 편하게 섭취할 수 있음
+풍부한 영양소 함량 — 기존 오쏘몰 이뮨 라인 대비 영양소가 다량 함유되어 있음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>믿을 수 있는 원료 — 영국산 비타민C 원료를 사용하여 품질 면에서 더욱 안심하고 섭취함
-확실한 체감 효과 — 매일 섭취 시 피부 상태 개선 및 체력 관리에 긍정적인 영향이 느껴짐</t>
+          <t>신뢰할 수 있는 원산지 — 영국산 고품질 비타민C 원료를 사용하여 안심하고 복용 가능함
+확실한 피부 컨디션 개선 — 복용 시 피부 상태와 신체 활력이 개선되는 것을 체감함</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4211,24 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>느린 배송 속도 — 배송이 도착하는 데 10일이나 소요되어 선물 전달 시 곤란함
-다소 부담스러운 가격 — 제품의 가격대가 다소 높게 책정되어 다소 아쉽게 느껴짐</t>
+          <t>심각한 배송 지연 — 배송이 최대 10일까지 늦어져 선물 전달에 차질이 생김
+다소 부담스러운 가격 — 타 비타민 제품에 비해 가격대가 다소 높게 느껴짐</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 액상 맛 — 제형의 농도가 진하고 액상 특성상 맛 자체는 다소 아쉬움</t>
+          <t>아쉬운 액상 맛 — 타 액상 영양제처럼 맛 자체는 뛰어난 편이 아님</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>다소 부실한 포장 — 전용 쇼핑백 없이 제품 박스만 덜렁 배송되어 선물용 포장으로는 아쉬움</t>
+          <t>아쉬운 포장 서비스 — 쇼핑백이 제공되지 않고 상자에만 담겨 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>다소 아쉬운 부피감 — 포장 크기가 콤팩트하여 시각적으로 매우 풍성한 느낌을 주지는 않음</t>
+          <t>부족한 볼륨감 — 소포장 구성 특성상 선물할 때 풍성한 느낌이 다소 덜함</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -4231,7 +4236,7 @@
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>매우 신맛과 아쉬운 맛 — 가루 제형 특유의 자극적인 신맛과 씁쓸함으로 인해 먹기가 힘듦</t>
+          <t>너무 자극적인 신맛 — 가루 제형에 산도가 매우 높아 섭취 시 신맛과 쓴맛의 거부감이 큼</t>
         </is>
       </c>
     </row>
@@ -4461,12 +4466,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4518,22 +4523,22 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>타이거모닝</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>타이거모닝</t>
         </is>
       </c>
     </row>
@@ -4575,22 +4580,22 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4643,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1691</v>
@@ -4656,16 +4661,16 @@
         <v>1535</v>
       </c>
       <c r="I19" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>1909</v>
+      </c>
+      <c r="K19" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>1179</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4676,70 +4681,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>훌륭하고 맛있는 맛 — 효소 제품임에도 특유의 거북한 향이 전혀 없고 아주 맛있음
-풍성한 콜라보 구성 — 아이돌 포토카드, 엽서 및 증정 단백질바까지 다채로운 구성품이 함께 제공됨</t>
+          <t>알찬 굿즈 및 사은품 — 포토카드와 엽서, 고단백질바 등 풍성하고 퀄리티 높은 사은품을 제공함
+거부감 없는 뛰어난 맛 — 효소 특유의 쿰쿰함 없이 맛있고 다양한 맛으로 즐길 수 있음
+깔끔하고 안전한 포장 — 내용물이 훼손되지 않도록 견고하게 잘 밀봉되어 배송됨</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 소화 개선 — 밀가루나 무거운 식사를 한 후 섭취하면 더부룩한 속이 한결 편안해짐
-구수한 고구마 맛 — 역한 맛없이 달콤하고 구수한 고구마 맛이 나서 온 가족이 맛있게 먹음
-알찬 사은품 혜택 — 파로 곡물바 및 차 제품이 증정품으로 추가 포함되어 만족스러움</t>
+          <t>탁월한 소화 개선 효과 — 밀가루 섭취 후 속이 더부룩할 때 복용하면 속이 편안해짐
+구수하고 친숙한 고구마맛 — 시큼하지 않고 구수한 고구마 맛이 나서 호불호 없이 먹을 수 있음
+넉넉한 사은품 증정 — 구매 시 견과류바와 추가 포가 증정되어 구성이 풍성함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>눈부신 오간자 포장 — 오간자 에디션 포장과 세트 플리츠백이 극도로 화려하고 예뻐 감격스러움
-비림 없는 맛과 효과 — 콜라겐 특유의 비린 맛 없이 상큼하고 맛있으며 피부 탄력 및 피로에 도움을 줌</t>
+          <t>감동을 주는 고급 포장 — 오간자 에디션과 플리츠백 등 패키지가 아주 세련되어 열어보는 즐거움이 있음
+맛있는 액상 콜라겐 — 비린 맛 없이 상큼하고 맛있어서 꾸준히 챙겨 먹기 좋음
+만족스러운 피로 완화 — 복용 시 평소보다 피로를 느끼는 빈도가 줄어드는 느낌을 받음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 맛 — 퍽퍽함이나 비린내가 전혀 느껴지지 않으며 식감이 매우 부드러움
-다채로운 양념 소스 — 떡볶이맛 등 다이어트 식단이라는 생각이 안 들 정도로 다양한 맛을 맛있게 즐김
-훌륭한 가성비 — 할인 혜택 적용 시 많은 수량의 구성품을 저렴한 가격에 쟁여두기 좋음</t>
+          <t>촉촉하고 부드러운 육질 — 닭가슴살 특유의 퍽퍽함 없이 수분감이 있어 섭취하기 좋음
+훌륭한 소스 맛과 다양성 — 떡볶이 맛 등 질리지 않는 다양한 소스로 구성되어 맛있는 식단 관리가 가능함
+매력적인 특가 구성 — 다양한 구성을 타 유통 채널 대비 합리적인 가격으로 구매 가능함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>신속한 숙취 완화 — 음주 전후 섭취 시 다음 날 머리가 무겁거나 피로한 숙취 증상이 눈에 띄게 줄어듦
-편리한 휴대와 포장 — 가볍고 작은 낱개 스틱으로 설계되어 가방에 넣고 다니다가 물 없이 짜 먹기 좋음
-품격 있는 패키지 — 고급스러운 보라색 박스 및 리본 끈 리플릿 포장으로 선물용 가치가 우수함</t>
+          <t>뛰어난 숙취 해소 효능 — 음주 전후 섭취 시 다음 날 아침 피로와 두통 등 숙취가 눈에 띄게 줄어듦
+고급스러운 보라빛 선물팩 — 전용 쇼핑백과 리본 디테일이 갖춰져 있어 선물하기에 대단히 품격 있음
+휴대에 용이한 스틱형 — 작고 가벼운 개별 스틱으로 가방이나 주머니에 넣어 다닐 수 있음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 아침에 가뿐하게 기상할 수 있고 운동할 때 지치지 않아 컨디션에 큰 도움을 줌
-완벽한 성분 조합 — 지친 간을 위한 밀크씨슬과 활력 증진용 아르기닌을 한 번에 챙길 수 있는 알찬 세트임
-넉넉한 용량 — 2개월분의 넉넉한 수량으로 구성되어 장기적인 관리가 수월함</t>
+          <t>완벽한 활력 영양 조합 — 활력 충전용 아르기닌과 간 건강용 밀크씨슬을 효율적으로 한 번에 챙길 수 있음
+우수한 일상 피로 개선 — 섭취 후 아침 기상이 가벼워지며 운동 집중력 향상에 큰 도움을 줌</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 쫄깃한 식감 — 닭가슴살 본연의 퍽퍽함을 탈피하여 쫄깃하고 속이 매우 부드러움
-다양한 맛과 적당한 간 — 간이 짜지 않고 적절하며 볼 형태와 소스 타입이 다양해 식단 관리가 지루하지 않음
-빠른 조리 편의성 — 전자레인지에 간단히 데우기만 하면 바로 먹을 수 있어 식사 시간이 단축됨</t>
+          <t>상큼한 과일생강 조합 — 생강 외 사과, 레몬 등이 혼합되어 과일주스처럼 상큼하게 섭취할 수 있음
+감각적이고 귀여운 병 — 한 손에 쏙 들어오는 미니 보틀 형태로 디자인이 깜찍해 소장 가치가 높음
+환절기 호흡기 관리 도움 — 목 잠김 현상이 줄어들고 몸을 따뜻하게 보호해 비염과 환절기 건강 관리에 유용함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 맛 — 매실, 알로에, 요구르트 등 역함이나 인공적인 향 없이 음료수처럼 맛있음
-운동 집중력 상승 — 수분 및 전해질 보충으로 운동 수행 능력과 에너지가 향상됨
-물에 잘 녹는 분말 — 차가운 물에도 가루 뭉침 없이 부드럽게 잘 풀려 음용하기 편함</t>
+          <t>입자의 우수한 용해성 — 가루 뭉침 현상 없이 찬물이나 프로틴 음료에 부드럽고 빠르게 잘 녹음
+확실한 운동 능력 상승 — 몇 주간 꾸준히 섭취 시 운동 수행 횟수가 증가하고 근육 피로 회복이 빨라짐
+편리한 스쿱 내장 구성 — 통 내부에 전용 계량 스쿱이 들어있어 매일 정량 복용하기 편리함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛없는 깔끔함 — 프로틴 특유의 텁텁하고 비린 뒷맛이 전혀 느껴지지 않고 청량함
-포만감 가득한 든든함 — 운동 후 혹은 간식이 당길 때 섭취하면 배가 든든하게 채워져 식단에 유용함
-달콤하고 부드러운 맛 — 모카초콜릿, 딸기초코 등 시판 초코우유나 커피음료와 유사한 훌륭한 맛을 구현함</t>
+          <t>부드럽고 촉촉한 육질 — 수분감을 가득 머금어 전혀 퍽퍽하지 않고 쫄깃하고 촉촉함
+간편한 한 입 크기 볼 — 닭가슴살볼이 한 입 크기로 만들어져 샐러드나 도시락 반찬으로 먹기 좋음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 부드러운 맛 — 생강 함량이 높음에도 사과, 파인애플 등이 섞여 과일 주스처럼 섭취가 부드러움
-기상 시 에너지 충전 — 공복에 섭취 시 위에 부담이 없고 온몸이 따뜻해지며 수면 부족 피로를 깨워줌
-소장하고 싶은 보틀 — 앙증맞고 귀여운 미니 병 형태로 보관이 편리하고 섭취 시 기분 전환에 도움을 줌</t>
+          <t>역대급으로 훌륭한 맛 — 매실, 알로에, 요구르트 등 맛의 완성도가 매우 높아 물처럼 부담 없이 맛있게 즐길 수 있음
+뛰어난 가루 풀림성 — 미세한 가루가 찬물에도 뭉치지 않고 빠르게 녹아들어 섭취가 용이함
+대용량의 합리적 가격 — 오랫동안 복용할 수 있는 넉넉한 분량이 제공되어 가성비가 아주 우수함</t>
         </is>
       </c>
     </row>
@@ -4749,44 +4754,44 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>다소 지연된 배송 — 주문 이후 수령할 때까지 대기 시간이 다소 길어 아쉬움</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>정가 구매 시의 부담감 — 할인을 하지 않을 때는 가격대가 다소 높게 느껴져 아쉬움</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>꽤 비싼 가격대 — 정가가 다소 높게 느껴져 주로 할인 행사 기간을 기다려 구매하게 됨</t>
+          <t>다소 값비싼 가격대 — 정가 기준으로 가격 부담이 커 할인 기간에만 구매를 고려하게 됨</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>선호 품목 누락 아쉬움 — 파우치형 그릴 제품 등 선호도가 높은 일부 라인업이 구성에서 빠져 아쉽음</t>
+          <t>일부 선호 종류의 누락 — 맛있는 파우치 그릴 제품 등 선호도가 높은 특정 구성이 빠져 있어 아쉬움</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>쓴맛에 대한 호불호 — 쌍화탕이나 칡, 헛개 같은 한약재 맛이 다소 진하게 풍겨 호불호가 갈릴 수 있음</t>
+          <t>호불호 갈리는 한약 맛 — 쌍화탕이나 약재 같은 씁쓸하고 진한 맛이 느껴져 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 마감 불량 — 선물용으로 동봉되는 전용 쇼핑백의 손잡이 끈이 조립되지 않은 채 누락되어 배송됨</t>
+          <t>사은품 쇼핑백 마감 불량 — 동봉된 선물용 쇼핑백의 손잡이 끈이 누락되어 오는 배송 하자가 발생함</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>약간의 배송 지연 — 주문 후 실제 수령하기까지 배송 속도가 다른 곳보다 다소 느렸음</t>
+          <t>다소 강한 생강의 자극 — 생강 함량이 높아 톡 쏘는 찡한 매운맛에 대해 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>매운 향에 따른 호불호 — 생강 본연의 톡 쏘는 아린 맛이 뒤에 남아 어린아이나 입맛에 따라 맵게 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 배송 지연 — 주문 후 수령하기까지 배송에 다소 시간이 소요되어 아쉬움</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4826,22 +4831,22 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t>29,900원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>31,500원</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>29,900원</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5036,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5039,62 +5044,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 면역엔 홍삼 필름 10매 10일분</t>
+          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911096&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/X3lfEnRBZWFGAzpNcACh610911096_00_01X3lfEnRBZWFGAzpNcACh.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/OqWOmDxWU1qoZh2gUZfq600000279_00_01OqWOmDxWU1qoZh2gUZfq.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>58</v>
+        <v>374</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>간편한 구강용해 필름 — 물 없이 입안에 붙이기만 하면 사르르 녹아내려 언제 어디서든 간편히 섭취함</t>
+          <t>극강의 구매 가성비 — 대기업 제약사의 성분을 저렴한 가격으로 누릴 수 있어 경제적 부담이 없음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>체감되는 건강 증진 — 지속해서 복용하면 피로가 덜하고 몸이 한결 건강해지는 보람이 있음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>지나치게 얇은 두께 — 필름이 너무 얇아 입천장에 닿자마자 순식간에 녹아 없어져 아쉬움</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>다소 씁쓸한 홍삼맛 — 홍삼 성분 배합으로 특유의 씁쓸하고 쓴 한방 맛이 감돌아 호불호가 있음</t>
-        </is>
-      </c>
+          <t>삼키기 쉬운 캡슐 크기 — 목넘김이 편안하도록 캡슐 크기가 작게 제작되어 섭취 시 부담이 없음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>부담 없는 미니 구성 — 6일분의 소량 포장으로 본인에게 맞는지 가볍게 테스트해 보기 좋음</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5102,54 +5103,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762105&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/6YtHsleJV0YMOtFdtOAk901762105_00_016YtHsleJV0YMOtFdtOAk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>241</v>
+        <v>792</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>경쟁력 있는 가격대 — 다이소 특유의 매우 저렴하고 뛰어난 가성비로 만족감을 안겨줌</t>
+          <t>간편한 혈당 케어 — 바나바잎 추출물이 함유되어 매일 손쉽게 식후 혈당을 관리할 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>부담 없는 달콤함 — 맛이 달콤하고 무난하여 홍삼을 처음 접해보는 비기너도 쉽게 복용함</t>
+          <t>높은 가격 접근성 — 저렴한 다이소 가격대로 혈당 관리 영양제를 입문하기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>아쉬운 10일 소포장 — 매일 장기 복용하려는 사용자에게는 10정 구성이 너무 적게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5157,12 +5162,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 당케어</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5172,35 +5177,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580761&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250610/qUVshiLfS5KUSiQ9T3cu591580761_00_05qUVshiLfS5KUSiQ9T3cu.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>821</v>
+        <v>7132</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>실속 가득한 가성비 — 아주 합리적인 가격선에서 고품질의 장 건강 유산균을 경험할 수 있음</t>
+          <t>독보적인 30일 가성비 — 한 달 복용량이 매우 저렴하게 구성되어 매달 고정 지출 부담을 최소화함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>휴대와 복용 편의성 — 개별 슬림 포장이라 외출 시 휴대하기 좋고 언제든 물 없이 털어먹음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>혈당과 장의 동시 관리 — 유산균 기본 기능인 장 활성화에 더해 혈당 케어까지 가능해 유용함</t>
-        </is>
-      </c>
+          <t>편리한 1일 1정 섭취 — 하루에 단 한 알만 챙겨 먹으면 되어 일상생활 중 복용하기 편리함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -5208,7 +5209,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5216,12 +5217,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5231,43 +5232,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618639&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260703/B8ckjHxaPLARUlbtHVdP601618639_00_02B8ckjHxaPLARUlbtHVdP.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>559</v>
+        <v>4162</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>신속한 활력 공급 — 야근이나 운동 전후 등 격렬히 지치고 졸릴 때 한 포로 기운을 북돋아 줌</t>
+          <t>합리적인 초저가 가격 — 가격 거품을 완전히 걷어내어 꾸준히 복용해도 금전적 부담이 전혀 없음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>비리지 않은 깔끔한 맛 — 아르기닌 특유의 비릿한 느낌이 없고 상큼하고 깔끔하여 목넘김이 좋음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>유용한 마그네슘 보충 — 마그네슘 부족으로 인한 미세한 눈가 떨림이 생겼을 때 보조 수단으로 수월함</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>건조하고 뻑뻑한 눈 관리 — 매일 복용 시 스마트폰이나 모니터로 인해 쌓인 눈의 피로감을 다스리는 데 도움을 줌</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>온라인 공식몰 품절 잦음 — 다이소 온라인 매장에서는 재고 수급이 원활하지 않아 직접 오프라인 매장을 가야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5275,51 +5276,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 홍삼＆비타B</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911030&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/xNJvNqGjAYp0B7f9QQ8M610911030_00_00xNJvNqGjAYp0B7f9QQ8M.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>138</v>
+        <v>6628</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 매우 저렴한 수준에 출시되어 가계 부담 없이 쉽게 매수하여 음용함</t>
+          <t>비린 맛 없는 목넘김 — 오메가3 고유의 역한 비린내가 거의 느껴지지 않고 캡슐 크기가 작아 삼키기 쉬움</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 기력 회복 — 오후에 유난히 몸이 지칠 때 가볍게 꺼내어 한 포 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>묽은 음료 형태의 농도 — 영양제 고농축 형태라기보다는 조금 싱겁고 물을 많이 탄 묽은 홍삼액 같음</t>
-        </is>
-      </c>
+          <t>믿을 수 없는 착한 가격 — 고가군에 속하는 rTG 오메가3를 매우 실속 있는 가격으로 경험할 수 있음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>일상적 피로감 완화 — 지속적으로 섭취 시 혈행 건강과 함께 일상적인 피로가 감소하는 것을 도움받음</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5334,7 +5335,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5349,43 +5350,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000147&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/7vBQfmyyR1zN9NfVg993600000147_00_007vBQfmyyR1zN9NfVg993.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>674</v>
+        <v>3829</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>최상의 가성비 영양제 — 시중 대형 브랜드 대비 월등히 저렴해 영양제를 꾸준히 먹기 수월함</t>
+          <t>원활한 배변 활동 지원 — 복용 후 장 운동이 활발해져 화장실을 한결 편안하고 원활하게 갈 수 있음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>높은 장기 복용 만족 — 품질이 가격 대비 만족스러워 자녀가 부모님께 수 차례 거듭 재구매해 선물함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>조금 연한 유효 성분 — 가성비 대비 훌륭하나 고함량 전문 제품 대비 절대적인 칼슘 성분 양은 부족함</t>
-        </is>
-      </c>
+          <t>높은 복용 편의성 — 여러 번 나누어 먹을 필요 없이 하루 한 알만 챙기면 되어 간편함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>최상의 저렴한 가격 — 다이어트 보조제를 고가로 구매할 필요 없이 알뜰하게 장만 가능함</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5393,49 +5394,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260930/WeHdQCGpAxVMhBizdMLr030086178_00_00WeHdQCGpAxVMhBizdMLr.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>109</v>
+        <v>931</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>편리한 다이소 쇼핑 — 필요한 물품을 한 번에 장바구니에 담아 가볍게 구입할 수 있어 동선이 편안함</t>
+          <t>중독성 있는 새콤한 맛 — 다소 시큼하지만 입맛을 돋우며 기존 타 비타민 분말 제품보다 맛이 뛰어남</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>가볍게 씹어 삼키는 환 — 삼켜야 하는 알약과 달리 한 입 베어 물고 가볍게 씹어 꿀꺽 삼키기 유용함</t>
+          <t>먹기 편한 고운 분말 제형 — 알약 형태가 아닌 입안에서 사르르 녹는 가루 형태라 섭취가 아주 즐거움</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>느끼기 어려운 빠른 효과 — 함유량이 대용량 대비 다소 약해 건강상 효능을 명확히 몸으로 실감하기에는 아쉬움</t>
+          <t>인기 폭발로 인한 품절 — 재고가 입고되면 즉시 매진될 정도로 품절 속도가 빨라 구매하기 까다로움</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5444,7 +5445,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5452,12 +5453,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5467,36 +5468,36 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1532</v>
+        <v>836</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>목넘김 좋은 작은 제형 — 캡슐 알약의 크기가 무척 작아 목에 걸리는 불편함 없이 한 번에 아주 쉽게 잘 삼킴</t>
+          <t>알뜰한 가성비 건강 관리 — 메이저 브랜드의 멀티비타민을 저렴하게 구매하여 효율적인 건강 관리가 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>유명 제조사에 대한 안심 — 국내 유명 대기업인 안국약품 상표가 적용되어 제품 퀄리티를 더욱 신뢰함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>다소 불투명한 체감력 — 눈 건강과 건조증 완화를 기대해 오랫동안 재구매했으나 체감되는 눈 건강 개선은 미미함</t>
-        </is>
-      </c>
+          <t>기본에 충실한 영양 성분 — 꼭 필요한 필수 미네랄과 멀티비타민의 권장량을 알차게 모두 채움</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>편리하고 위생적인 용기 — 한 알씩 위생적으로 간편히 꺼내서 삼킬 수 있는 구조로 디자인됨</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5511,7 +5512,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5526,37 +5527,33 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>151</v>
+        <v>2825</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>막힘없이 도착하는 배송 — 구매 접수 이후 배송 과정이 지연 없이 발 빠르게 완료되어 좋음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>과식 후 체중 증가 방지 — 야식을 먹거나 과식을 한 이후에 섭취 시 몸무게가 크게 늘어나지 않게 유지해 줌</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>뛰어난 체중 감량 보조 — 식단 관리 및 체중 조절과 병행하여 복용 시 감량에 부가적인 시너지를 냄</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>다소 협소한 구성 기간 — 7일간의 짧은 용량 분량이라 건강 기능성의 체감을 확인하기엔 기간이 매우 부족함</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>다소 높은 체감 단가 — 다이소 내 타 카테고리 대비 공급 수량 기준 판매 가격대가 다소 높게 다가옴</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
@@ -5570,12 +5567,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5585,33 +5582,33 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1249</v>
+        <v>177</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>초소형 캡슐 알약 — 알약 형태가 무척 큰 기존 타사 제품들과 달리 목구멍을 쉽게 통과하도록 미니멀하게 설계됨</t>
+          <t>쓰지 않고 순한 보양 환 — 전통 침향환 특유의 지나친 쓴맛이 많이 억제되어 섭취 시 입안이 텁텁하지 않고 부드러움</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>거품 없는 염가 판매 — 불필요한 과도 포장을 제외하여 시중가에 비해 엄청나게 저렴한 비용으로 구매함</t>
+          <t>뛰어난 천연 활력 충전 — 환절기나 피로감이 누적되었을 때 아침 공복에 한 알 복용하면 기운이 충전됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>부담 없는 뼈 건강 관리 — 꾸준히 아침저녁 챙겨 삼키면 무릎 및 연골 뼈 건강관리에 기여를 하는 만족이 큼</t>
+          <t>입문하기 최적인 착한 가격 — 고가 약재인 침향을 다이소용 가성비 패키지로 가볍게 구매해 복용할 수 있음</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -5729,42 +5726,42 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5786,52 +5783,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>휴럼</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -5843,52 +5840,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 면역엔 홍삼 필름 10매 10일분</t>
+          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 당케어</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 홍삼＆비타B</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5896,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5908,25 +5905,25 @@
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5936,34 +5933,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>58</v>
+        <v>374</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>241</v>
+        <v>792</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>821</v>
+        <v>7132</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>559</v>
+        <v>4162</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>138</v>
+        <v>6628</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>674</v>
+        <v>3829</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>109</v>
+        <v>931</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1532</v>
+        <v>836</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>151</v>
+        <v>2825</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1249</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5974,108 +5971,97 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>간편한 구강용해 필름 — 물 없이 입안에 붙이기만 하면 사르르 녹아내려 언제 어디서든 간편히 섭취함
-체감되는 건강 증진 — 지속해서 복용하면 피로가 덜하고 몸이 한결 건강해지는 보람이 있음</t>
+          <t>극강의 구매 가성비 — 대기업 제약사의 성분을 저렴한 가격으로 누릴 수 있어 경제적 부담이 없음
+삼키기 쉬운 캡슐 크기 — 목넘김이 편안하도록 캡슐 크기가 작게 제작되어 섭취 시 부담이 없음
+부담 없는 미니 구성 — 6일분의 소량 포장으로 본인에게 맞는지 가볍게 테스트해 보기 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>경쟁력 있는 가격대 — 다이소 특유의 매우 저렴하고 뛰어난 가성비로 만족감을 안겨줌
-부담 없는 달콤함 — 맛이 달콤하고 무난하여 홍삼을 처음 접해보는 비기너도 쉽게 복용함</t>
+          <t>간편한 혈당 케어 — 바나바잎 추출물이 함유되어 매일 손쉽게 식후 혈당을 관리할 수 있음
+높은 가격 접근성 — 저렴한 다이소 가격대로 혈당 관리 영양제를 입문하기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>실속 가득한 가성비 — 아주 합리적인 가격선에서 고품질의 장 건강 유산균을 경험할 수 있음
-휴대와 복용 편의성 — 개별 슬림 포장이라 외출 시 휴대하기 좋고 언제든 물 없이 털어먹음
-혈당과 장의 동시 관리 — 유산균 기본 기능인 장 활성화에 더해 혈당 케어까지 가능해 유용함</t>
+          <t>독보적인 30일 가성비 — 한 달 복용량이 매우 저렴하게 구성되어 매달 고정 지출 부담을 최소화함
+편리한 1일 1정 섭취 — 하루에 단 한 알만 챙겨 먹으면 되어 일상생활 중 복용하기 편리함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>신속한 활력 공급 — 야근이나 운동 전후 등 격렬히 지치고 졸릴 때 한 포로 기운을 북돋아 줌
-비리지 않은 깔끔한 맛 — 아르기닌 특유의 비릿한 느낌이 없고 상큼하고 깔끔하여 목넘김이 좋음
-유용한 마그네슘 보충 — 마그네슘 부족으로 인한 미세한 눈가 떨림이 생겼을 때 보조 수단으로 수월함</t>
+          <t>합리적인 초저가 가격 — 가격 거품을 완전히 걷어내어 꾸준히 복용해도 금전적 부담이 전혀 없음
+건조하고 뻑뻑한 눈 관리 — 매일 복용 시 스마트폰이나 모니터로 인해 쌓인 눈의 피로감을 다스리는 데 도움을 줌</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 매우 저렴한 수준에 출시되어 가계 부담 없이 쉽게 매수하여 음용함
-간편한 기력 회복 — 오후에 유난히 몸이 지칠 때 가볍게 꺼내어 한 포 마시기 좋음</t>
+          <t>비린 맛 없는 목넘김 — 오메가3 고유의 역한 비린내가 거의 느껴지지 않고 캡슐 크기가 작아 삼키기 쉬움
+믿을 수 없는 착한 가격 — 고가군에 속하는 rTG 오메가3를 매우 실속 있는 가격으로 경험할 수 있음
+일상적 피로감 완화 — 지속적으로 섭취 시 혈행 건강과 함께 일상적인 피로가 감소하는 것을 도움받음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>최상의 가성비 영양제 — 시중 대형 브랜드 대비 월등히 저렴해 영양제를 꾸준히 먹기 수월함
-높은 장기 복용 만족 — 품질이 가격 대비 만족스러워 자녀가 부모님께 수 차례 거듭 재구매해 선물함</t>
+          <t>원활한 배변 활동 지원 — 복용 후 장 운동이 활발해져 화장실을 한결 편안하고 원활하게 갈 수 있음
+높은 복용 편의성 — 여러 번 나누어 먹을 필요 없이 하루 한 알만 챙기면 되어 간편함
+최상의 저렴한 가격 — 다이어트 보조제를 고가로 구매할 필요 없이 알뜰하게 장만 가능함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>편리한 다이소 쇼핑 — 필요한 물품을 한 번에 장바구니에 담아 가볍게 구입할 수 있어 동선이 편안함
-가볍게 씹어 삼키는 환 — 삼켜야 하는 알약과 달리 한 입 베어 물고 가볍게 씹어 꿀꺽 삼키기 유용함</t>
+          <t>중독성 있는 새콤한 맛 — 다소 시큼하지만 입맛을 돋우며 기존 타 비타민 분말 제품보다 맛이 뛰어남
+먹기 편한 고운 분말 제형 — 알약 형태가 아닌 입안에서 사르르 녹는 가루 형태라 섭취가 아주 즐거움</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>목넘김 좋은 작은 제형 — 캡슐 알약의 크기가 무척 작아 목에 걸리는 불편함 없이 한 번에 아주 쉽게 잘 삼킴
-유명 제조사에 대한 안심 — 국내 유명 대기업인 안국약품 상표가 적용되어 제품 퀄리티를 더욱 신뢰함</t>
+          <t>알뜰한 가성비 건강 관리 — 메이저 브랜드의 멀티비타민을 저렴하게 구매하여 효율적인 건강 관리가 가능함
+기본에 충실한 영양 성분 — 꼭 필요한 필수 미네랄과 멀티비타민의 권장량을 알차게 모두 채움
+편리하고 위생적인 용기 — 한 알씩 위생적으로 간편히 꺼내서 삼킬 수 있는 구조로 디자인됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>막힘없이 도착하는 배송 — 구매 접수 이후 배송 과정이 지연 없이 발 빠르게 완료되어 좋음</t>
+          <t>과식 후 체중 증가 방지 — 야식을 먹거나 과식을 한 이후에 섭취 시 몸무게가 크게 늘어나지 않게 유지해 줌
+뛰어난 체중 감량 보조 — 식단 관리 및 체중 조절과 병행하여 복용 시 감량에 부가적인 시너지를 냄</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>초소형 캡슐 알약 — 알약 형태가 무척 큰 기존 타사 제품들과 달리 목구멍을 쉽게 통과하도록 미니멀하게 설계됨
-거품 없는 염가 판매 — 불필요한 과도 포장을 제외하여 시중가에 비해 엄청나게 저렴한 비용으로 구매함
-부담 없는 뼈 건강 관리 — 꾸준히 아침저녁 챙겨 삼키면 무릎 및 연골 뼈 건강관리에 기여를 하는 만족이 큼</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>쓰지 않고 순한 보양 환 — 전통 침향환 특유의 지나친 쓴맛이 많이 억제되어 섭취 시 입안이 텁텁하지 않고 부드러움
+뛰어난 천연 활력 충전 — 환절기나 피로감이 누적되었을 때 아침 공복에 한 알 복용하면 기운이 충전됨
+입문하기 최적인 착한 가격 — 고가 약재인 침향을 다이소용 가성비 패키지로 가볍게 구매해 복용할 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>지나치게 얇은 두께 — 필름이 너무 얇아 입천장에 닿자마자 순식간에 녹아 없어져 아쉬움
-다소 씁쓸한 홍삼맛 — 홍삼 성분 배합으로 특유의 씁쓸하고 쓴 한방 맛이 감돌아 호불호가 있음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 10일 소포장 — 매일 장기 복용하려는 사용자에게는 10정 구성이 너무 적게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>묽은 음료 형태의 농도 — 영양제 고농축 형태라기보다는 조금 싱겁고 물을 많이 탄 묽은 홍삼액 같음</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>조금 연한 유효 성분 — 가성비 대비 훌륭하나 고함량 전문 제품 대비 절대적인 칼슘 성분 양은 부족함</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>온라인 공식몰 품절 잦음 — 다이소 온라인 매장에서는 재고 수급이 원활하지 않아 직접 오프라인 매장을 가야 하는 번거로움이 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>느끼기 어려운 빠른 효과 — 함유량이 대용량 대비 다소 약해 건강상 효능을 명확히 몸으로 실감하기에는 아쉬움</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>다소 불투명한 체감력 — 눈 건강과 건조증 완화를 기대해 오랫동안 재구매했으나 체감되는 눈 건강 개선은 미미함</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>다소 협소한 구성 기간 — 7일간의 짧은 용량 분량이라 건강 기능성의 체감을 확인하기엔 기간이 매우 부족함
-다소 높은 체감 단가 — 다이소 내 타 카테고리 대비 공급 수량 기준 판매 가격대가 다소 높게 다가옴</t>
-        </is>
-      </c>
+          <t>인기 폭발로 인한 품절 — 재고가 입고되면 즉시 매진될 정도로 품절 속도가 빨라 구매하기 까다로움</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6086,37 +6072,37 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -6353,7 +6339,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6361,27 +6347,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6396,7 +6382,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6404,27 +6390,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>59,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6439,7 +6425,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6447,34 +6433,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5491</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>쫀득하고 맛있는 식감 — 상큼한 레몬라임이나 복숭아 맛의 쫀득한 젤리로, 물 없이 언제 어디서나 섭취할 수 있음</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>합리적이고 알뜰한 세일 — 올리브영 세일 기간에 쿠폰을 적용하면 정가 대비 가성비가 매우 훌륭해 부담이 적음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>간편한 피부 장벽 케어 — 간식처럼 하나씩 씹어 먹는 것만으로도 고함량 저분자 콜라겐을 알차게 공급받음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6482,7 +6484,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6490,27 +6492,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>24,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166201ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6525,7 +6527,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6533,35 +6535,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>16158</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6572,7 +6570,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6580,27 +6578,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BNR17 다이어트유산균 비에날씬플러스 30포x3박스 (3개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>비에날씬</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>208,000원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000155805&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0015/B00000015580506ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6623,38 +6621,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>메디트리 바이탈포켓 비타민 7종 택1</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>메디트리</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,500원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268771&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026877101ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>16174</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>강력한 수면 유도 효과 — 뒤척임이 심하거나 불면으로 고민할 때 섭취하면 빠르게 숙면을 취하도록 도와줌</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>안심하고 먹는 식물성 — 정제가 아닌 젤리 타입이며 자연 유래 식물성 멜라토닌을 사용해 매일 안전하게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>소장 욕구 부르는 사은품 — 잠만보 말랑볼과 같이 실물로 소장하고 싶어지는 깜찍한 캐릭터 굿즈 구성을 증정함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6662,7 +6672,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6670,46 +6680,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>세노비스 피부촉촉 히알루론산 50ml*10/20병 (20일분)</t>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>세노비스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28,500원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000165293&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000002944&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016529310ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0000/A00000000294414ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>5682</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>21813</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>검증된 독보적 브랜드 — 대한민국 비타민 시장 1등인 고려은단의 메인 라인업이라 고민 없이 믿고 안전하게 선택함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>넉넉한 4개월 대용량 — 120정 구성으로 한 번 구비하면 여러 달 동안 꾸준히 고함량 비타민C를 수급할 수 있음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 효과 — 매일 챙겨 먹으면 일상의 나른함이 많이 감소하고 체력이 개선되는 효과를 봄</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>다소 큰 알약의 신맛 — 정제가 다소 크고 혓바닥에 닿을 때 시큼한 맛이 나서 삼키기 전에 자극이 될 수 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6717,46 +6743,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>뉴오리진 이너플로라 60캡슐 기획(+ 이노시톨 3포 증정)(2개월분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>뉴오리진</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248551&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024855105ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>4154</v>
+        <v>25749</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>우수한 질 유산균 효과 — 공복에 꼬박꼬박 정기적으로 삼켰을 때 체내 균형 등 개선 만족도가 무척 높음</t>
+          <t>질과 장의 이중 관리 — 유산균 섭취를 통해 여성의 민감한 질 환경 개선과 소화 장 건강을 한 번에 정밀 관리함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>간결하고 조그만 알약 — 성분은 알차지만 캡슐 크기는 아주 미니멀해 매일 아침 수월하게 목넘김이 됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>초소형 크기의 목넘김 — 캡슐 크기가 약 170mg으로 아주 미세하고 가벼워 약을 삼키지 못하는 사람도 부담 없이 섭취함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>깜찍한 포켓몬 한정판 — 카드 케이스 등 고품질 포켓몬 콜라보 랜덤 사은품이 동봉되어 소장 가치를 높임</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6877,47 +6907,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -6934,47 +6964,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>비에날씬</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>메디트리</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>세노비스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>뉴오리진</t>
+          <t>지노마스터</t>
         </is>
       </c>
     </row>
@@ -6991,47 +7021,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>BNR17 다이어트유산균 비에날씬플러스 30포x3박스 (3개월분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>메디트리 바이탈포켓 비타민 7종 택1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>세노비스 피부촉촉 히알루론산 50ml*10/20병 (20일분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>뉴오리진 이너플로라 60캡슐 기획(+ 이노시톨 3포 증정)(2개월분)</t>
         </is>
       </c>
     </row>
@@ -7044,17 +7074,17 @@
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.9</v>
@@ -7069,23 +7099,23 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>5491</v>
+      </c>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
-        <v>16158</v>
-      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>16174</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5682</v>
+        <v>21813</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4154</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>25749</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7094,16 +7124,35 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>쫀득하고 맛있는 식감 — 상큼한 레몬라임이나 복숭아 맛의 쫀득한 젤리로, 물 없이 언제 어디서나 섭취할 수 있음
+합리적이고 알뜰한 세일 — 올리브영 세일 기간에 쿠폰을 적용하면 정가 대비 가성비가 매우 훌륭해 부담이 적음
+간편한 피부 장벽 케어 — 간식처럼 하나씩 씹어 먹는 것만으로도 고함량 저분자 콜라겐을 알차게 공급받음</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>강력한 수면 유도 효과 — 뒤척임이 심하거나 불면으로 고민할 때 섭취하면 빠르게 숙면을 취하도록 도와줌
+안심하고 먹는 식물성 — 정제가 아닌 젤리 타입이며 자연 유래 식물성 멜라토닌을 사용해 매일 안전하게 먹을 수 있음
+소장 욕구 부르는 사은품 — 잠만보 말랑볼과 같이 실물로 소장하고 싶어지는 깜찍한 캐릭터 굿즈 구성을 증정함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>검증된 독보적 브랜드 — 대한민국 비타민 시장 1등인 고려은단의 메인 라인업이라 고민 없이 믿고 안전하게 선택함
+넉넉한 4개월 대용량 — 120정 구성으로 한 번 구비하면 여러 달 동안 꾸준히 고함량 비타민C를 수급할 수 있음
+확실한 피로 회복 효과 — 매일 챙겨 먹으면 일상의 나른함이 많이 감소하고 체력이 개선되는 효과를 봄</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>우수한 질 유산균 효과 — 공복에 꼬박꼬박 정기적으로 삼켰을 때 체내 균형 등 개선 만족도가 무척 높음
-간결하고 조그만 알약 — 성분은 알차지만 캡슐 크기는 아주 미니멀해 매일 아침 수월하게 목넘김이 됨</t>
+          <t>질과 장의 이중 관리 — 유산균 섭취를 통해 여성의 민감한 질 환경 개선과 소화 장 건강을 한 번에 정밀 관리함
+초소형 크기의 목넘김 — 캡슐 크기가 약 170mg으로 아주 미세하고 가벼워 약을 삼키지 못하는 사람도 부담 없이 섭취함
+깜찍한 포켓몬 한정판 — 카드 케이스 등 고품질 포켓몬 콜라보 랜덤 사은품이 동봉되어 소장 가치를 높임</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7170,11 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약의 신맛 — 정제가 다소 크고 혓바닥에 닿을 때 시큼한 맛이 나서 삼키기 전에 자극이 될 수 있음</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7137,47 +7190,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>59,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>24,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>27,400원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>16,200원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>208,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,500원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>28,500원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>39,900원</t>
         </is>
       </c>
     </row>
@@ -7307,10 +7360,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -7319,7 +7372,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7329,16 +7382,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -7360,16 +7413,16 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7379,54 +7432,54 @@
         <v>12.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7439,10 +7492,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -7451,13 +7504,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7467,19 +7520,19 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7489,10 +7542,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
